--- a/02_HRvLR_groups/04_Modules/01_Contrasts/c_data/02_contrasts.xlsx
+++ b/02_HRvLR_groups/04_Modules/01_Contrasts/c_data/02_contrasts.xlsx
@@ -12,16 +12,15 @@
     <sheet name="fry_tests" sheetId="3" r:id="rId3"/>
     <sheet name="membership_contrast" sheetId="4" r:id="rId4"/>
     <sheet name="correlation" sheetId="5" r:id="rId5"/>
-    <sheet name="ancova" sheetId="6" r:id="rId6"/>
-    <sheet name="input_manifest" sheetId="7" r:id="rId7"/>
-    <sheet name="package_versions" sheetId="8" r:id="rId8"/>
+    <sheet name="input_manifest" sheetId="6" r:id="rId6"/>
+    <sheet name="package_versions" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="201">
   <si>
     <t>sheet</t>
   </si>
@@ -53,12 +52,6 @@
     <t>Within-subject correlation on the eigengenes and on limpa's matrix.</t>
   </si>
   <si>
-    <t>ancova</t>
-  </si>
-  <si>
-    <t>ANCOVA per module and window on eigengenes: arm effect at equal start, t, p, BH, Storey q.</t>
-  </si>
-  <si>
     <t>input_manifest</t>
   </si>
   <si>
@@ -189,27 +182,6 @@
   </si>
   <si>
     <t>limpa</t>
-  </si>
-  <si>
-    <t>feature</t>
-  </si>
-  <si>
-    <t>window</t>
-  </si>
-  <si>
-    <t>n_HR</t>
-  </si>
-  <si>
-    <t>n_LR</t>
-  </si>
-  <si>
-    <t>effect</t>
-  </si>
-  <si>
-    <t>acute</t>
-  </si>
-  <si>
-    <t>training</t>
   </si>
   <si>
     <t>input</t>
@@ -993,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -1050,14 +1022,6 @@
       </c>
       <c r="B7" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1072,33 +1036,33 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>0.01283078020949423</v>
@@ -1118,10 +1082,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
       </c>
       <c r="C3">
         <v>0.09440445000396436</v>
@@ -1141,10 +1105,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>0.1840363438694336</v>
@@ -1164,10 +1128,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0.1198520105819541</v>
@@ -1187,10 +1151,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>0.05625010267267194</v>
@@ -1210,10 +1174,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0.03741195069636757</v>
@@ -1233,10 +1197,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>0.04563211403653972</v>
@@ -1256,10 +1220,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>0.07677850999334784</v>
@@ -1279,10 +1243,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>-0.1066665954609026</v>
@@ -1302,10 +1266,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>-0.02564785024043283</v>
@@ -1325,10 +1289,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>0.06091873266916135</v>
@@ -1348,10 +1312,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>-0.04359920384876288</v>
@@ -1371,10 +1335,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>-0.01651924447606348</v>
@@ -1394,10 +1358,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <v>-0.1164290016074944</v>
@@ -1417,10 +1381,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>-0.09990665905565829</v>
@@ -1440,10 +1404,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <v>0.1329960102884896</v>
@@ -1463,10 +1427,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>0.03081044135253759</v>
@@ -1486,10 +1450,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>0.0923381414153735</v>
@@ -1509,10 +1473,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>0.1188870913039811</v>
@@ -1532,10 +1496,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21">
         <v>-0.0126737123653535</v>
@@ -1555,10 +1519,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>0.03831868511400581</v>
@@ -1578,10 +1542,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <v>0.03437082432538882</v>
@@ -1601,10 +1565,10 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>-0.05623007947741086</v>
@@ -1624,10 +1588,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>-0.03070499109460353</v>
@@ -1647,10 +1611,10 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>0.04265662288230938</v>
@@ -1670,10 +1634,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <v>0.00777710046891119</v>
@@ -1693,10 +1657,10 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C28">
         <v>0.08971717184103782</v>
@@ -1716,10 +1680,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <v>0.008660071962696393</v>
@@ -1739,10 +1703,10 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C30">
         <v>-0.03172793519459035</v>
@@ -1762,10 +1726,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <v>-0.02127077203710268</v>
@@ -1785,10 +1749,10 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32">
         <v>0.1165682519256543</v>
@@ -1808,10 +1772,10 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C33">
         <v>-0.1540167894504817</v>
@@ -1831,10 +1795,10 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C34">
         <v>-0.1598701476483494</v>
@@ -1854,10 +1818,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C35">
         <v>-0.003760551082807956</v>
@@ -1877,10 +1841,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C36">
         <v>-0.1741907012174949</v>
@@ -1900,10 +1864,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37">
         <v>-0.09820715634925017</v>
@@ -1923,10 +1887,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C38">
         <v>-0.0969772183359263</v>
@@ -1946,10 +1910,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C39">
         <v>-0.03985691067597131</v>
@@ -1969,10 +1933,10 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C40">
         <v>0.08170786940152622</v>
@@ -1992,10 +1956,10 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C41">
         <v>0.212089054649029</v>
@@ -2015,10 +1979,10 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C42">
         <v>0.1491486630984593</v>
@@ -2038,10 +2002,10 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C43">
         <v>0.1106110263117505</v>
@@ -2061,10 +2025,10 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C44">
         <v>-0.1984069844606098</v>
@@ -2084,10 +2048,10 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C45">
         <v>0.08304341409008191</v>
@@ -2107,10 +2071,10 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C46">
         <v>0.09861847503806193</v>
@@ -2130,10 +2094,10 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C47">
         <v>-0.08420751898914591</v>
@@ -2153,10 +2117,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C48">
         <v>-0.07796093750331676</v>
@@ -2176,10 +2140,10 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C49">
         <v>-0.0112495873685874</v>
@@ -2199,10 +2163,10 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C50">
         <v>-0.1559874645716707</v>
@@ -2222,10 +2186,10 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C51">
         <v>-0.1428063646399321</v>
@@ -2245,10 +2209,10 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C52">
         <v>-0.1014931880628585</v>
@@ -2268,10 +2232,10 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C53">
         <v>-0.009262561566248877</v>
@@ -2291,10 +2255,10 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C54">
         <v>0.1221034738367436</v>
@@ -2314,10 +2278,10 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C55">
         <v>0.1175362688340187</v>
@@ -2337,10 +2301,10 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C56">
         <v>0.07987109856058568</v>
@@ -2360,10 +2324,10 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C57">
         <v>0.1059766480074679</v>
@@ -2383,10 +2347,10 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C58">
         <v>-0.1263038238514167</v>
@@ -2406,10 +2370,10 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C59">
         <v>-0.09083089983759275</v>
@@ -2429,10 +2393,10 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C60">
         <v>-0.02371627426246552</v>
@@ -2452,10 +2416,10 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C61">
         <v>-0.06306153379485273</v>
@@ -2475,10 +2439,10 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C62">
         <v>0.08948853304878628</v>
@@ -2498,10 +2462,10 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C63">
         <v>0.01884211636587637</v>
@@ -2521,10 +2485,10 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C64">
         <v>-0.08288104230866983</v>
@@ -2544,10 +2508,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C65">
         <v>0.006120322391442438</v>
@@ -2567,10 +2531,10 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C66">
         <v>-0.08554947035930749</v>
@@ -2590,10 +2554,10 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C67">
         <v>0.0461696866591752</v>
@@ -2613,10 +2577,10 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C68">
         <v>-0.06905449886029885</v>
@@ -2636,10 +2600,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C69">
         <v>-0.1361677119102748</v>
@@ -2659,10 +2623,10 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C70">
         <v>0.05032078107205568</v>
@@ -2682,10 +2646,10 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C71">
         <v>0.008062674442809455</v>
@@ -2705,10 +2669,10 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C72">
         <v>-0.03309775627468109</v>
@@ -2728,10 +2692,10 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C73">
         <v>0.07471622907116816</v>
@@ -2751,10 +2715,10 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C74">
         <v>0.009692608096674014</v>
@@ -2774,10 +2738,10 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C75">
         <v>0.02952267147546299</v>
@@ -2797,10 +2761,10 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C76">
         <v>0.04665809512146761</v>
@@ -2820,10 +2784,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C77">
         <v>-0.03067669703020915</v>
@@ -2843,10 +2807,10 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C78">
         <v>0.08243612501730313</v>
@@ -2866,10 +2830,10 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C79">
         <v>0.008817160145390274</v>
@@ -2889,10 +2853,10 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C80">
         <v>0.007085241669415418</v>
@@ -2912,10 +2876,10 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C81">
         <v>-0.01662565532128205</v>
@@ -2935,10 +2899,10 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C82">
         <v>0.04526295224153696</v>
@@ -2958,10 +2922,10 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C83">
         <v>-0.05779320914914794</v>
@@ -2981,10 +2945,10 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C84">
         <v>-0.003159122439516068</v>
@@ -3004,10 +2968,10 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C85">
         <v>-0.0256408232942434</v>
@@ -3027,10 +2991,10 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C86">
         <v>-0.06024179867993276</v>
@@ -3050,10 +3014,10 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C87">
         <v>0.02004387592556908</v>
@@ -3073,10 +3037,10 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C88">
         <v>-0.05860014661863253</v>
@@ -3096,10 +3060,10 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C89">
         <v>-0.01548670834208585</v>
@@ -3119,10 +3083,10 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C90">
         <v>-0.05517839493744107</v>
@@ -3142,10 +3106,10 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C91">
         <v>-0.03197779189708801</v>
@@ -3165,10 +3129,10 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C92">
         <v>0.1700990738845911</v>
@@ -3188,10 +3152,10 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C93">
         <v>0.00638027307013822</v>
@@ -3211,10 +3175,10 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C94">
         <v>-0.1398034001343717</v>
@@ -3234,10 +3198,10 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C95">
         <v>0.1593121551582781</v>
@@ -3257,10 +3221,10 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C96">
         <v>-0.0480099918988449</v>
@@ -3280,10 +3244,10 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C97">
         <v>0.0485489839551453</v>
@@ -3303,10 +3267,10 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C98">
         <v>-0.1455078659188254</v>
@@ -3326,10 +3290,10 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C99">
         <v>-0.1651195069522309</v>
@@ -3349,10 +3313,10 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C100">
         <v>-0.06146922272673586</v>
@@ -3372,10 +3336,10 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C101">
         <v>0.07197615740851056</v>
@@ -3395,10 +3359,10 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C102">
         <v>0.06321589101656049</v>
@@ -3418,10 +3382,10 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C103">
         <v>0.1783147035445347</v>
@@ -3441,10 +3405,10 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C104">
         <v>-0.1230627929651029</v>
@@ -3464,10 +3428,10 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C105">
         <v>0.05158129341510637</v>
@@ -3487,10 +3451,10 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C106">
         <v>0.1297022169358266</v>
@@ -3510,10 +3474,10 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C107">
         <v>-0.1201652300789954</v>
@@ -3533,10 +3497,10 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B108" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C108">
         <v>0.06359400865142675</v>
@@ -3556,10 +3520,10 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C109">
         <v>0.09169820245406007</v>
@@ -3579,10 +3543,10 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B110" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C110">
         <v>0.0009649192779729726</v>
@@ -3602,10 +3566,10 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C111">
         <v>0.06892381503802544</v>
@@ -3625,10 +3589,10 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C112">
         <v>-0.0009067344176382428</v>
@@ -3648,10 +3612,10 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B113" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C113">
         <v>0.0112612897111509</v>
@@ -3671,10 +3635,10 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C114">
         <v>0.1330085894707587</v>
@@ -3694,10 +3658,10 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C115">
         <v>-0.07596160436629908</v>
@@ -3717,10 +3681,10 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B116" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C116">
         <v>-0.06830447312274221</v>
@@ -3740,10 +3704,10 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C117">
         <v>0.05314163220025016</v>
@@ -3763,10 +3727,10 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B118" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C118">
         <v>-0.1333163756898007</v>
@@ -3786,10 +3750,10 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B119" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C119">
         <v>-0.02517931643875987</v>
@@ -3809,10 +3773,10 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B120" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C120">
         <v>-0.08470106641290405</v>
@@ -3832,10 +3796,10 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B121" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C121">
         <v>-0.07863588701855562</v>
@@ -3855,10 +3819,10 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C122">
         <v>0.2007757709148003</v>
@@ -3878,10 +3842,10 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C123">
         <v>-0.07605585194716491</v>
@@ -3901,10 +3865,10 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C124">
         <v>-0.148620560279762</v>
@@ -3924,10 +3888,10 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B125" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C125">
         <v>0.1522269134888627</v>
@@ -3947,10 +3911,10 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C126">
         <v>-0.03138433657756286</v>
@@ -3970,10 +3934,10 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B127" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C127">
         <v>0.003286031713608348</v>
@@ -3993,10 +3957,10 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C128">
         <v>-0.08771465676967743</v>
@@ -4016,10 +3980,10 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B129" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C129">
         <v>-0.1619603845127149</v>
@@ -4039,10 +4003,10 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C130">
         <v>-0.03582839943249246</v>
@@ -4062,10 +4026,10 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C131">
         <v>0.1322179560884433</v>
@@ -4085,10 +4049,10 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B132" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C132">
         <v>0.04317201509099143</v>
@@ -4108,10 +4072,10 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C133">
         <v>0.2369148501631672</v>
@@ -4131,10 +4095,10 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C134">
         <v>-0.107576084623017</v>
@@ -4154,10 +4118,10 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B135" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C135">
         <v>0.1067596883525474</v>
@@ -4177,10 +4141,10 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C136">
         <v>0.1616800088329147</v>
@@ -4210,39 +4174,39 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E2">
         <v>0.7212891524899173</v>
@@ -4256,16 +4220,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
       </c>
       <c r="C3">
         <v>222</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3">
         <v>0.2383167762685479</v>
@@ -4279,16 +4243,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E4">
         <v>0.006785567259288519</v>
@@ -4302,16 +4266,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5">
         <v>0.1248757866555617</v>
@@ -4325,16 +4289,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E6">
         <v>0.459337993930822</v>
@@ -4348,16 +4312,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7">
         <v>0.616179343438038</v>
@@ -4371,16 +4335,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8">
         <v>0.6330659022808024</v>
@@ -4394,16 +4358,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9">
         <v>0.3101777782942107</v>
@@ -4417,16 +4381,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10">
         <v>0.1841674048208421</v>
@@ -4440,16 +4404,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11">
         <v>0.7549608298399599</v>
@@ -4463,16 +4427,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E12">
         <v>0.332792471429519</v>
@@ -4486,16 +4450,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E13">
         <v>0.6743862986508345</v>
@@ -4509,16 +4473,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E14">
         <v>0.6896724079556116</v>
@@ -4532,16 +4496,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <v>285</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E15">
         <v>0.1305968224167157</v>
@@ -4555,16 +4519,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E16">
         <v>0.1863077697203323</v>
@@ -4578,16 +4542,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E17">
         <v>0.05174091321313593</v>
@@ -4601,16 +4565,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>222</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E18">
         <v>0.6977197930628782</v>
@@ -4624,16 +4588,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>172</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E19">
         <v>0.08344051149644224</v>
@@ -4647,16 +4611,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E20">
         <v>0.1491894867172493</v>
@@ -4670,16 +4634,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E21">
         <v>0.8599591921986931</v>
@@ -4693,16 +4657,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E22">
         <v>0.7983591226649546</v>
@@ -4716,16 +4680,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E23">
         <v>0.6465204077645061</v>
@@ -4739,16 +4703,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E24">
         <v>0.3722777794155656</v>
@@ -4762,16 +4726,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E25">
         <v>0.6786880077879309</v>
@@ -4785,16 +4749,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E26">
         <v>0.5271393404318152</v>
@@ -4808,16 +4772,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E27">
         <v>0.8500537905606765</v>
@@ -4831,16 +4795,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C28">
         <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E28">
         <v>0.259824123087828</v>
@@ -4854,16 +4818,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E29">
         <v>0.8030984878396401</v>
@@ -4877,16 +4841,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C30">
         <v>285</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E30">
         <v>0.6046751318381907</v>
@@ -4900,16 +4864,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E31">
         <v>0.6545415514273677</v>
@@ -4923,16 +4887,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E32">
         <v>0.1289777729514826</v>
@@ -4946,16 +4910,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C33">
         <v>222</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E33">
         <v>0.04568045539229165</v>
@@ -4969,16 +4933,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C34">
         <v>172</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E34">
         <v>0.01710750388137697</v>
@@ -4992,16 +4956,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C35">
         <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E35">
         <v>0.9602637457033212</v>
@@ -5015,16 +4979,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C36">
         <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E36">
         <v>0.02115173511840629</v>
@@ -5038,16 +5002,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37">
         <v>57</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E37">
         <v>0.2256979553862191</v>
@@ -5061,16 +5025,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C38">
         <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E38">
         <v>0.2433766480008816</v>
@@ -5084,16 +5048,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C39">
         <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E39">
         <v>0.5037223373771056</v>
@@ -5107,16 +5071,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C40">
         <v>89</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E40">
         <v>0.2523737164132895</v>
@@ -5130,16 +5094,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C41">
         <v>58</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E41">
         <v>0.002871480108214769</v>
@@ -5153,16 +5117,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C42">
         <v>104</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E42">
         <v>0.0242224971966647</v>
@@ -5176,16 +5140,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C43">
         <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E43">
         <v>0.1837276935714727</v>
@@ -5199,16 +5163,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C44">
         <v>54</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E44">
         <v>0.008074715225002894</v>
@@ -5222,16 +5186,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C45">
         <v>285</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E45">
         <v>0.284767349390875</v>
@@ -5245,16 +5209,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C46">
         <v>137</v>
       </c>
       <c r="D46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E46">
         <v>0.1941531261987327</v>
@@ -5268,16 +5232,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C47">
         <v>100</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E47">
         <v>0.3308431489644973</v>
@@ -5291,16 +5255,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C48">
         <v>222</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E48">
         <v>0.3940818119848993</v>
@@ -5314,16 +5278,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C49">
         <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E49">
         <v>0.6795453960214415</v>
@@ -5337,16 +5301,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C50">
         <v>41</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E50">
         <v>0.1040101727542565</v>
@@ -5360,16 +5324,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C51">
         <v>115</v>
       </c>
       <c r="D51" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E51">
         <v>0.08747146145874972</v>
@@ -5383,16 +5347,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C52">
         <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E52">
         <v>0.3838797287254099</v>
@@ -5406,16 +5370,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C53">
         <v>78</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E53">
         <v>0.8355018579477747</v>
@@ -5429,16 +5393,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C54">
         <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E54">
         <v>0.1857148371001019</v>
@@ -5452,16 +5416,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C55">
         <v>89</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E55">
         <v>0.1906158826570442</v>
@@ -5475,16 +5439,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C56">
         <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E56">
         <v>0.3641123217575316</v>
@@ -5498,16 +5462,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C57">
         <v>104</v>
       </c>
       <c r="D57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E57">
         <v>0.2238840452411751</v>
@@ -5521,16 +5485,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C58">
         <v>43</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E58">
         <v>0.1872348527267419</v>
@@ -5544,16 +5508,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C59">
         <v>54</v>
       </c>
       <c r="D59" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E59">
         <v>0.1890565972671015</v>
@@ -5567,16 +5531,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C60">
         <v>285</v>
       </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E60">
         <v>0.8496407500546881</v>
@@ -5590,16 +5554,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C61">
         <v>137</v>
       </c>
       <c r="D61" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E61">
         <v>0.5598658841496271</v>
@@ -5613,16 +5577,16 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C62">
         <v>100</v>
       </c>
       <c r="D62" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E62">
         <v>0.2789033209322663</v>
@@ -5636,16 +5600,16 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C63">
         <v>222</v>
       </c>
       <c r="D63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E63">
         <v>0.8091820582896769</v>
@@ -5659,16 +5623,16 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C64">
         <v>172</v>
       </c>
       <c r="D64" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E64">
         <v>0.3560921507029264</v>
@@ -5682,16 +5646,16 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C65">
         <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E65">
         <v>0.8736694175073125</v>
@@ -5705,16 +5669,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C66">
         <v>115</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E66">
         <v>0.3034200707527884</v>
@@ -5728,16 +5692,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C67">
         <v>57</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E67">
         <v>0.5488784019176287</v>
@@ -5751,16 +5715,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C68">
         <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E68">
         <v>0.4499148550798032</v>
@@ -5774,16 +5738,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C69">
         <v>41</v>
       </c>
       <c r="D69" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E69">
         <v>0.1119978447994941</v>
@@ -5797,16 +5761,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C70">
         <v>89</v>
       </c>
       <c r="D70" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E70">
         <v>0.491689121421325</v>
@@ -5820,16 +5784,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C71">
         <v>58</v>
       </c>
       <c r="D71" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E71">
         <v>0.9785475134385477</v>
@@ -5843,16 +5807,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C72">
         <v>104</v>
       </c>
       <c r="D72" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E72">
         <v>0.6482230872887182</v>
@@ -5866,16 +5830,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C73">
         <v>43</v>
       </c>
       <c r="D73" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E73">
         <v>0.4460166555845311</v>
@@ -5889,16 +5853,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C74">
         <v>54</v>
       </c>
       <c r="D74" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E74">
         <v>0.8310417558664527</v>
@@ -5912,16 +5876,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C75">
         <v>285</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E75">
         <v>0.7268685447492459</v>
@@ -5935,16 +5899,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C76">
         <v>137</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E76">
         <v>0.6726627494524084</v>
@@ -5958,16 +5922,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C77">
         <v>100</v>
       </c>
       <c r="D77" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E77">
         <v>0.6993042636191225</v>
@@ -5981,16 +5945,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C78">
         <v>222</v>
       </c>
       <c r="D78" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E78">
         <v>0.3186092344920337</v>
@@ -6004,16 +5968,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C79">
         <v>172</v>
       </c>
       <c r="D79" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E79">
         <v>0.8995586232674084</v>
@@ -6027,16 +5991,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C80">
         <v>41</v>
       </c>
       <c r="D80" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E80">
         <v>0.9861248791936312</v>
@@ -6050,16 +6014,16 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C81">
         <v>115</v>
       </c>
       <c r="D81" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E81">
         <v>0.8569099700724805</v>
@@ -6073,16 +6037,16 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C82">
         <v>57</v>
       </c>
       <c r="D82" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E82">
         <v>0.407484828320495</v>
@@ -6096,16 +6060,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C83">
         <v>78</v>
       </c>
       <c r="D83" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E83">
         <v>0.4828660557197831</v>
@@ -6119,16 +6083,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C84">
         <v>41</v>
       </c>
       <c r="D84" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E84">
         <v>0.8803303638620392</v>
@@ -6142,16 +6106,16 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C85">
         <v>89</v>
       </c>
       <c r="D85" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E85">
         <v>0.8099679716010696</v>
@@ -6165,16 +6129,16 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C86">
         <v>58</v>
       </c>
       <c r="D86" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E86">
         <v>0.3976996022287111</v>
@@ -6188,16 +6152,16 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C87">
         <v>104</v>
       </c>
       <c r="D87" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E87">
         <v>0.7685412191553561</v>
@@ -6211,16 +6175,16 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C88">
         <v>43</v>
       </c>
       <c r="D88" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E88">
         <v>0.5186186868191891</v>
@@ -6234,16 +6198,16 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C89">
         <v>54</v>
       </c>
       <c r="D89" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E89">
         <v>0.7134391117651796</v>
@@ -6257,16 +6221,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C90">
         <v>285</v>
       </c>
       <c r="D90" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E90">
         <v>0.5335325264236641</v>
@@ -6280,16 +6244,16 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C91">
         <v>137</v>
       </c>
       <c r="D91" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E91">
         <v>0.6620026884146492</v>
@@ -6303,16 +6267,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C92">
         <v>100</v>
       </c>
       <c r="D92" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E92">
         <v>0.04787067101862517</v>
@@ -6326,16 +6290,16 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C93">
         <v>222</v>
       </c>
       <c r="D93" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E93">
         <v>0.9976837494942394</v>
@@ -6349,16 +6313,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C94">
         <v>172</v>
       </c>
       <c r="D94" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E94">
         <v>0.10045223016043</v>
@@ -6372,16 +6336,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C95">
         <v>41</v>
       </c>
       <c r="D95" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E95">
         <v>0.1106851665534353</v>
@@ -6395,16 +6359,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C96">
         <v>115</v>
       </c>
       <c r="D96" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E96">
         <v>0.5797699685328501</v>
@@ -6418,16 +6382,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C97">
         <v>57</v>
       </c>
       <c r="D97" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E97">
         <v>0.5434519471562713</v>
@@ -6441,16 +6405,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C98">
         <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E98">
         <v>0.1308942846224253</v>
@@ -6464,16 +6428,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C99">
         <v>41</v>
       </c>
       <c r="D99" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E99">
         <v>0.07748585821862124</v>
@@ -6487,16 +6451,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C100">
         <v>89</v>
       </c>
       <c r="D100" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E100">
         <v>0.6054604722195142</v>
@@ -6510,16 +6474,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C101">
         <v>58</v>
       </c>
       <c r="D101" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E101">
         <v>0.2789089894092113</v>
@@ -6533,16 +6497,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C102">
         <v>104</v>
       </c>
       <c r="D102" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E102">
         <v>0.2576151993777915</v>
@@ -6556,16 +6520,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C103">
         <v>43</v>
       </c>
       <c r="D103" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E103">
         <v>0.05433673280361322</v>
@@ -6579,16 +6543,16 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C104">
         <v>54</v>
       </c>
       <c r="D104" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E104">
         <v>0.1334912379463427</v>
@@ -6602,16 +6566,16 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C105">
         <v>285</v>
       </c>
       <c r="D105" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E105">
         <v>0.5545526015936439</v>
@@ -6625,16 +6589,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C106">
         <v>137</v>
       </c>
       <c r="D106" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E106">
         <v>0.1770360004733135</v>
@@ -6648,16 +6612,16 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C107">
         <v>100</v>
       </c>
       <c r="D107" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E107">
         <v>0.2687683182609541</v>
@@ -6671,16 +6635,16 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B108" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C108">
         <v>222</v>
       </c>
       <c r="D108" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E108">
         <v>0.5528277440647307</v>
@@ -6694,16 +6658,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C109">
         <v>172</v>
       </c>
       <c r="D109" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E109">
         <v>0.4182138613741564</v>
@@ -6717,16 +6681,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B110" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C110">
         <v>41</v>
       </c>
       <c r="D110" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E110">
         <v>0.9055848353358569</v>
@@ -6740,16 +6704,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C111">
         <v>115</v>
       </c>
       <c r="D111" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E111">
         <v>0.5135979711851908</v>
@@ -6763,16 +6727,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C112">
         <v>57</v>
       </c>
       <c r="D112" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E112">
         <v>0.8558460954963459</v>
@@ -6786,16 +6750,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B113" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C113">
         <v>78</v>
       </c>
       <c r="D113" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E113">
         <v>0.9718574171232152</v>
@@ -6809,16 +6773,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C114">
         <v>41</v>
       </c>
       <c r="D114" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E114">
         <v>0.1806570589693548</v>
@@ -6832,16 +6796,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C115">
         <v>89</v>
       </c>
       <c r="D115" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E115">
         <v>0.4932884722620819</v>
@@ -6855,16 +6819,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B116" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C116">
         <v>58</v>
       </c>
       <c r="D116" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E116">
         <v>0.5029064217353116</v>
@@ -6878,16 +6842,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C117">
         <v>104</v>
       </c>
       <c r="D117" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E117">
         <v>0.561114513645794</v>
@@ -6901,16 +6865,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B118" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C118">
         <v>43</v>
       </c>
       <c r="D118" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E118">
         <v>0.2798710506870293</v>
@@ -6924,16 +6888,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B119" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C119">
         <v>54</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E119">
         <v>0.6478003162965866</v>
@@ -6947,16 +6911,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B120" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C120">
         <v>285</v>
       </c>
       <c r="D120" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E120">
         <v>0.4546192937171517</v>
@@ -6970,16 +6934,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B121" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C121">
         <v>137</v>
       </c>
       <c r="D121" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E121">
         <v>0.5120971728173007</v>
@@ -6993,16 +6957,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C122">
         <v>100</v>
       </c>
       <c r="D122" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E122">
         <v>0.0735114005190117</v>
@@ -7016,16 +6980,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C123">
         <v>222</v>
       </c>
       <c r="D123" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E123">
         <v>0.4568699685911753</v>
@@ -7039,16 +7003,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C124">
         <v>172</v>
       </c>
       <c r="D124" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E124">
         <v>0.1724842543035282</v>
@@ -7062,16 +7026,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B125" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C125">
         <v>41</v>
       </c>
       <c r="D125" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E125">
         <v>0.211358826887555</v>
@@ -7085,16 +7049,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C126">
         <v>115</v>
       </c>
       <c r="D126" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E126">
         <v>0.7687510249692784</v>
@@ -7108,16 +7072,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B127" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C127">
         <v>57</v>
       </c>
       <c r="D127" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E127">
         <v>0.8733119368285702</v>
@@ -7131,16 +7095,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C128">
         <v>78</v>
       </c>
       <c r="D128" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E128">
         <v>0.510826202673432</v>
@@ -7154,16 +7118,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B129" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C129">
         <v>41</v>
       </c>
       <c r="D129" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E129">
         <v>0.1338187302191925</v>
@@ -7177,16 +7141,16 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C130">
         <v>89</v>
       </c>
       <c r="D130" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E130">
         <v>0.8147038522604922</v>
@@ -7200,16 +7164,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C131">
         <v>58</v>
       </c>
       <c r="D131" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E131">
         <v>0.1481413769911368</v>
@@ -7223,16 +7187,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B132" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C132">
         <v>104</v>
       </c>
       <c r="D132" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E132">
         <v>0.517353766908045</v>
@@ -7246,16 +7210,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C133">
         <v>43</v>
       </c>
       <c r="D133" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E133">
         <v>0.05158628368848495</v>
@@ -7269,16 +7233,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C134">
         <v>54</v>
       </c>
       <c r="D134" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E134">
         <v>0.3881916833403307</v>
@@ -7292,16 +7256,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B135" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C135">
         <v>285</v>
       </c>
       <c r="D135" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E135">
         <v>0.3636972214625617</v>
@@ -7315,16 +7279,16 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C136">
         <v>137</v>
       </c>
       <c r="D136" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E136">
         <v>0.176331446216194</v>
@@ -7348,27 +7312,27 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>285</v>
@@ -7382,10 +7346,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
         <v>37</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
       </c>
       <c r="C3">
         <v>285</v>
@@ -7399,10 +7363,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>285</v>
@@ -7416,10 +7380,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>285</v>
@@ -7433,10 +7397,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>285</v>
@@ -7450,10 +7414,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>285</v>
@@ -7467,10 +7431,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8">
         <v>285</v>
@@ -7484,10 +7448,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9">
         <v>285</v>
@@ -7501,10 +7465,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10">
         <v>285</v>
@@ -7518,10 +7482,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>43</v>
@@ -7535,10 +7499,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>43</v>
@@ -7552,10 +7516,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>43</v>
@@ -7569,10 +7533,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>43</v>
@@ -7586,10 +7550,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>43</v>
@@ -7603,10 +7567,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>43</v>
@@ -7620,10 +7584,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>43</v>
@@ -7637,10 +7601,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>43</v>
@@ -7654,10 +7618,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>43</v>
@@ -7671,10 +7635,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20">
         <v>58</v>
@@ -7688,10 +7652,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21">
         <v>58</v>
@@ -7705,10 +7669,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22">
         <v>58</v>
@@ -7722,10 +7686,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>58</v>
@@ -7739,10 +7703,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24">
         <v>58</v>
@@ -7756,10 +7720,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25">
         <v>58</v>
@@ -7773,10 +7737,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C26">
         <v>58</v>
@@ -7790,10 +7754,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C27">
         <v>58</v>
@@ -7807,10 +7771,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C28">
         <v>58</v>
@@ -7824,10 +7788,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C29">
         <v>54</v>
@@ -7841,10 +7805,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>54</v>
@@ -7858,10 +7822,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <v>54</v>
@@ -7875,10 +7839,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>54</v>
@@ -7892,10 +7856,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C33">
         <v>54</v>
@@ -7909,10 +7873,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>54</v>
@@ -7926,10 +7890,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C35">
         <v>54</v>
@@ -7943,10 +7907,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C36">
         <v>54</v>
@@ -7960,10 +7924,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C37">
         <v>54</v>
@@ -7977,10 +7941,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C38">
         <v>222</v>
@@ -7994,10 +7958,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C39">
         <v>222</v>
@@ -8011,10 +7975,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C40">
         <v>222</v>
@@ -8028,10 +7992,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C41">
         <v>222</v>
@@ -8045,10 +8009,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C42">
         <v>222</v>
@@ -8062,10 +8026,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C43">
         <v>222</v>
@@ -8079,10 +8043,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C44">
         <v>222</v>
@@ -8096,10 +8060,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C45">
         <v>222</v>
@@ -8113,10 +8077,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C46">
         <v>222</v>
@@ -8130,10 +8094,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C47">
         <v>104</v>
@@ -8147,10 +8111,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48">
         <v>104</v>
@@ -8164,10 +8128,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C49">
         <v>104</v>
@@ -8181,10 +8145,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C50">
         <v>104</v>
@@ -8198,10 +8162,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C51">
         <v>104</v>
@@ -8215,10 +8179,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C52">
         <v>104</v>
@@ -8232,10 +8196,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C53">
         <v>104</v>
@@ -8249,10 +8213,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C54">
         <v>104</v>
@@ -8266,10 +8230,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C55">
         <v>104</v>
@@ -8283,10 +8247,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C56">
         <v>172</v>
@@ -8300,10 +8264,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C57">
         <v>172</v>
@@ -8317,10 +8281,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C58">
         <v>172</v>
@@ -8334,10 +8298,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C59">
         <v>172</v>
@@ -8351,10 +8315,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C60">
         <v>172</v>
@@ -8368,10 +8332,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C61">
         <v>172</v>
@@ -8385,10 +8349,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C62">
         <v>172</v>
@@ -8402,10 +8366,10 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C63">
         <v>172</v>
@@ -8419,10 +8383,10 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C64">
         <v>172</v>
@@ -8436,10 +8400,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C65">
         <v>41</v>
@@ -8453,10 +8417,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C66">
         <v>41</v>
@@ -8470,10 +8434,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C67">
         <v>41</v>
@@ -8487,10 +8451,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B68" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C68">
         <v>41</v>
@@ -8504,10 +8468,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B69" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C69">
         <v>41</v>
@@ -8521,10 +8485,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C70">
         <v>41</v>
@@ -8538,10 +8502,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C71">
         <v>41</v>
@@ -8555,10 +8519,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B72" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C72">
         <v>41</v>
@@ -8572,10 +8536,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73">
         <v>41</v>
@@ -8589,10 +8553,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B74" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C74">
         <v>100</v>
@@ -8606,10 +8570,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C75">
         <v>100</v>
@@ -8623,10 +8587,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C76">
         <v>100</v>
@@ -8640,10 +8604,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B77" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C77">
         <v>100</v>
@@ -8657,10 +8621,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C78">
         <v>100</v>
@@ -8674,10 +8638,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C79">
         <v>100</v>
@@ -8691,10 +8655,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C80">
         <v>100</v>
@@ -8708,10 +8672,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C81">
         <v>100</v>
@@ -8725,10 +8689,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C82">
         <v>100</v>
@@ -8742,10 +8706,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C83">
         <v>115</v>
@@ -8759,10 +8723,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B84" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C84">
         <v>115</v>
@@ -8776,10 +8740,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B85" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C85">
         <v>115</v>
@@ -8793,10 +8757,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B86" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C86">
         <v>115</v>
@@ -8810,10 +8774,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B87" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C87">
         <v>115</v>
@@ -8827,10 +8791,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B88" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C88">
         <v>115</v>
@@ -8844,10 +8808,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B89" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C89">
         <v>115</v>
@@ -8861,10 +8825,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B90" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C90">
         <v>115</v>
@@ -8878,10 +8842,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C91">
         <v>115</v>
@@ -8895,10 +8859,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C92">
         <v>57</v>
@@ -8912,10 +8876,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C93">
         <v>57</v>
@@ -8929,10 +8893,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C94">
         <v>57</v>
@@ -8946,10 +8910,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C95">
         <v>57</v>
@@ -8963,10 +8927,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C96">
         <v>57</v>
@@ -8980,10 +8944,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C97">
         <v>57</v>
@@ -8997,10 +8961,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C98">
         <v>57</v>
@@ -9014,10 +8978,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C99">
         <v>57</v>
@@ -9031,10 +8995,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C100">
         <v>57</v>
@@ -9048,10 +9012,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B101" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C101">
         <v>137</v>
@@ -9065,10 +9029,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B102" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C102">
         <v>137</v>
@@ -9082,10 +9046,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
+        <v>36</v>
+      </c>
+      <c r="B103" t="s">
         <v>38</v>
-      </c>
-      <c r="B103" t="s">
-        <v>40</v>
       </c>
       <c r="C103">
         <v>137</v>
@@ -9099,10 +9063,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B104" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C104">
         <v>137</v>
@@ -9116,10 +9080,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B105" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C105">
         <v>137</v>
@@ -9133,10 +9097,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B106" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C106">
         <v>137</v>
@@ -9150,10 +9114,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C107">
         <v>137</v>
@@ -9167,10 +9131,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B108" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C108">
         <v>137</v>
@@ -9184,10 +9148,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C109">
         <v>137</v>
@@ -9201,10 +9165,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B110" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C110">
         <v>89</v>
@@ -9218,10 +9182,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C111">
         <v>89</v>
@@ -9235,10 +9199,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B112" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C112">
         <v>89</v>
@@ -9252,10 +9216,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B113" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C113">
         <v>89</v>
@@ -9269,10 +9233,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C114">
         <v>89</v>
@@ -9286,10 +9250,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B115" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C115">
         <v>89</v>
@@ -9303,10 +9267,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B116" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C116">
         <v>89</v>
@@ -9320,10 +9284,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B117" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C117">
         <v>89</v>
@@ -9337,10 +9301,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B118" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C118">
         <v>89</v>
@@ -9354,10 +9318,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C119">
         <v>78</v>
@@ -9371,10 +9335,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C120">
         <v>78</v>
@@ -9388,10 +9352,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B121" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C121">
         <v>78</v>
@@ -9405,10 +9369,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B122" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C122">
         <v>78</v>
@@ -9422,10 +9386,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B123" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C123">
         <v>78</v>
@@ -9439,10 +9403,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B124" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C124">
         <v>78</v>
@@ -9456,10 +9420,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B125" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C125">
         <v>78</v>
@@ -9473,10 +9437,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B126" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C126">
         <v>78</v>
@@ -9490,10 +9454,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B127" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C127">
         <v>78</v>
@@ -9507,10 +9471,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C128">
         <v>41</v>
@@ -9524,10 +9488,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C129">
         <v>41</v>
@@ -9541,10 +9505,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C130">
         <v>41</v>
@@ -9558,10 +9522,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C131">
         <v>41</v>
@@ -9575,10 +9539,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C132">
         <v>41</v>
@@ -9592,10 +9556,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B133" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C133">
         <v>41</v>
@@ -9609,10 +9573,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C134">
         <v>41</v>
@@ -9626,10 +9590,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C135">
         <v>41</v>
@@ -9643,10 +9607,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C136">
         <v>41</v>
@@ -9670,7 +9634,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -9678,7 +9642,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>0.03669198762791754</v>
@@ -9686,7 +9650,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B3">
         <v>0.1698778207668435</v>
@@ -9699,906 +9663,73 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1">
+    <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>60</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>8</v>
-      </c>
-      <c r="E2">
-        <v>0.149622450720365</v>
-      </c>
-      <c r="F2">
-        <v>1.830698711660787</v>
-      </c>
-      <c r="G2">
-        <v>0.0727136394611739</v>
-      </c>
-      <c r="H2">
-        <v>0.2392268659557643</v>
-      </c>
-      <c r="I2">
-        <v>0.2392268659557643</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>-0.03126096767776449</v>
-      </c>
-      <c r="F3">
-        <v>-0.3815983189034482</v>
-      </c>
-      <c r="G3">
-        <v>0.7042697176327881</v>
-      </c>
-      <c r="H3">
-        <v>0.7042697176327881</v>
-      </c>
-      <c r="I3">
-        <v>0.7042697176327881</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>-0.124194804335903</v>
-      </c>
-      <c r="F4">
-        <v>-1.536447794487877</v>
-      </c>
-      <c r="G4">
-        <v>0.1303180840743474</v>
-      </c>
-      <c r="H4">
-        <v>0.2792530373021731</v>
-      </c>
-      <c r="I4">
-        <v>0.2792530373021731</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>0.1462760287313176</v>
-      </c>
-      <c r="F5">
-        <v>1.945576447969002</v>
-      </c>
-      <c r="G5">
-        <v>0.05696412312773258</v>
-      </c>
-      <c r="H5">
-        <v>0.2392268659557643</v>
-      </c>
-      <c r="I5">
-        <v>0.2392268659557643</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>-0.03644564154524167</v>
-      </c>
-      <c r="F6">
-        <v>-0.4835745309248124</v>
-      </c>
-      <c r="G6">
-        <v>0.6306598829588922</v>
-      </c>
-      <c r="H6">
-        <v>0.6757070174559558</v>
-      </c>
-      <c r="I6">
-        <v>0.6757070174559558</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>0.0493196484014369</v>
-      </c>
-      <c r="F7">
-        <v>0.6567560395598976</v>
-      </c>
-      <c r="G7">
-        <v>0.514151125164047</v>
-      </c>
-      <c r="H7">
-        <v>0.6757070174559558</v>
-      </c>
-      <c r="I7">
-        <v>0.6757070174559558</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8">
-        <v>8</v>
-      </c>
-      <c r="E8">
-        <v>-0.1442532831705063</v>
-      </c>
-      <c r="F8">
-        <v>-1.786126848421769</v>
-      </c>
-      <c r="G8">
-        <v>0.07974228865192143</v>
-      </c>
-      <c r="H8">
-        <v>0.2392268659557643</v>
-      </c>
-      <c r="I8">
-        <v>0.2392268659557643</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9">
-        <v>7</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9">
-        <v>-0.1458444525961809</v>
-      </c>
-      <c r="F9">
-        <v>-1.802489578797228</v>
-      </c>
-      <c r="G9">
-        <v>0.07709867879650618</v>
-      </c>
-      <c r="H9">
-        <v>0.2392268659557643</v>
-      </c>
-      <c r="I9">
-        <v>0.2392268659557643</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-      <c r="D10">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>-0.05524999188949415</v>
-      </c>
-      <c r="F10">
-        <v>-0.7444320766015292</v>
-      </c>
-      <c r="G10">
-        <v>0.4598703773956038</v>
-      </c>
-      <c r="H10">
-        <v>0.6757070174559558</v>
-      </c>
-      <c r="I10">
-        <v>0.6757070174559558</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>8</v>
-      </c>
-      <c r="E11">
-        <v>0.0509977954890793</v>
-      </c>
-      <c r="F11">
-        <v>0.5431159793773894</v>
-      </c>
-      <c r="G11">
-        <v>0.5893041887289965</v>
-      </c>
-      <c r="H11">
-        <v>0.6757070174559558</v>
-      </c>
-      <c r="I11">
-        <v>0.6757070174559558</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>8</v>
-      </c>
-      <c r="E12">
-        <v>0.05132210377434869</v>
-      </c>
-      <c r="F12">
-        <v>0.632815362419997</v>
-      </c>
-      <c r="G12">
-        <v>0.5295480142480629</v>
-      </c>
-      <c r="H12">
-        <v>0.6757070174559558</v>
-      </c>
-      <c r="I12">
-        <v>0.6757070174559558</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-      <c r="D13">
-        <v>8</v>
-      </c>
-      <c r="E13">
-        <v>0.1533257086067223</v>
-      </c>
-      <c r="F13">
-        <v>1.823553755235289</v>
-      </c>
-      <c r="G13">
-        <v>0.07380397592820787</v>
-      </c>
-      <c r="H13">
-        <v>0.2392268659557643</v>
-      </c>
-      <c r="I13">
-        <v>0.2392268659557643</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-      <c r="D14">
-        <v>8</v>
-      </c>
-      <c r="E14">
-        <v>-0.110185370715539</v>
-      </c>
-      <c r="F14">
-        <v>-1.280547925445209</v>
-      </c>
-      <c r="G14">
-        <v>0.2058726800381598</v>
-      </c>
-      <c r="H14">
-        <v>0.3860112750715497</v>
-      </c>
-      <c r="I14">
-        <v>0.3860112750715497</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-      <c r="D15">
-        <v>8</v>
-      </c>
-      <c r="E15">
-        <v>0.0504045912251412</v>
-      </c>
-      <c r="F15">
-        <v>0.6155934104072067</v>
-      </c>
-      <c r="G15">
-        <v>0.5407711902672454</v>
-      </c>
-      <c r="H15">
-        <v>0.6757070174559558</v>
-      </c>
-      <c r="I15">
-        <v>0.6757070174559558</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-      <c r="D16">
-        <v>8</v>
-      </c>
-      <c r="E16">
-        <v>0.1243896425671077</v>
-      </c>
-      <c r="F16">
-        <v>1.585758464163546</v>
-      </c>
-      <c r="G16">
-        <v>0.1186836980318369</v>
-      </c>
-      <c r="H16">
-        <v>0.2792530373021731</v>
-      </c>
-      <c r="I16">
-        <v>0.2792530373021731</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17">
-        <v>6</v>
-      </c>
-      <c r="D17">
-        <v>8</v>
-      </c>
-      <c r="E17">
-        <v>-0.07559942457093886</v>
-      </c>
-      <c r="F17">
-        <v>-0.9096400294343769</v>
-      </c>
-      <c r="G17">
-        <v>0.3675169803228983</v>
-      </c>
-      <c r="H17">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I17">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18">
-        <v>6</v>
-      </c>
-      <c r="D18">
-        <v>8</v>
-      </c>
-      <c r="E18">
-        <v>0.07197140552399961</v>
-      </c>
-      <c r="F18">
-        <v>1.004082153757619</v>
-      </c>
-      <c r="G18">
-        <v>0.320329174384404</v>
-      </c>
-      <c r="H18">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I18">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19">
-        <v>6</v>
-      </c>
-      <c r="D19">
-        <v>8</v>
-      </c>
-      <c r="E19">
-        <v>0.04204234456756108</v>
-      </c>
-      <c r="F19">
-        <v>0.5659039782155296</v>
-      </c>
-      <c r="G19">
-        <v>0.5740717150651711</v>
-      </c>
-      <c r="H19">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I19">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20">
-        <v>6</v>
-      </c>
-      <c r="D20">
-        <v>8</v>
-      </c>
-      <c r="E20">
-        <v>0.007838078140885859</v>
-      </c>
-      <c r="F20">
-        <v>0.1051489835892471</v>
-      </c>
-      <c r="G20">
-        <v>0.916691848843291</v>
-      </c>
-      <c r="H20">
-        <v>0.9821698380463832</v>
-      </c>
-      <c r="I20">
-        <v>0.9821698380463832</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21">
-        <v>6</v>
-      </c>
-      <c r="D21">
-        <v>8</v>
-      </c>
-      <c r="E21">
-        <v>-0.06292643254614574</v>
-      </c>
-      <c r="F21">
-        <v>-0.8211195979601441</v>
-      </c>
-      <c r="G21">
-        <v>0.4156015814042689</v>
-      </c>
-      <c r="H21">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I21">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22">
-        <v>6</v>
-      </c>
-      <c r="D22">
-        <v>8</v>
-      </c>
-      <c r="E22">
-        <v>0.0009810424327508847</v>
-      </c>
-      <c r="F22">
-        <v>0.01184592140360972</v>
-      </c>
-      <c r="G22">
-        <v>0.9905972035918902</v>
-      </c>
-      <c r="H22">
-        <v>0.9905972035918902</v>
-      </c>
-      <c r="I22">
-        <v>0.9905972035918902</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23">
-        <v>6</v>
-      </c>
-      <c r="D23">
-        <v>8</v>
-      </c>
-      <c r="E23">
-        <v>-0.05639925390662026</v>
-      </c>
-      <c r="F23">
-        <v>-0.7515650429972033</v>
-      </c>
-      <c r="G23">
-        <v>0.4559492755090305</v>
-      </c>
-      <c r="H23">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I23">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24">
-        <v>6</v>
-      </c>
-      <c r="D24">
-        <v>8</v>
-      </c>
-      <c r="E24">
-        <v>0.05028674100447091</v>
-      </c>
-      <c r="F24">
-        <v>0.6410217031434399</v>
-      </c>
-      <c r="G24">
-        <v>0.5245302865471666</v>
-      </c>
-      <c r="H24">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I24">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
-      <c r="D25">
-        <v>8</v>
-      </c>
-      <c r="E25">
-        <v>-0.02007628832009806</v>
-      </c>
-      <c r="F25">
-        <v>-0.2634025669201787</v>
-      </c>
-      <c r="G25">
-        <v>0.7933577002915425</v>
-      </c>
-      <c r="H25">
-        <v>0.9821698380463832</v>
-      </c>
-      <c r="I25">
-        <v>0.9821698380463832</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26">
-        <v>6</v>
-      </c>
-      <c r="D26">
-        <v>8</v>
-      </c>
-      <c r="E26">
-        <v>-0.05622934750228478</v>
-      </c>
-      <c r="F26">
-        <v>-0.8307294310709609</v>
-      </c>
-      <c r="G26">
-        <v>0.4102029572714337</v>
-      </c>
-      <c r="H26">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I26">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27">
-        <v>6</v>
-      </c>
-      <c r="D27">
-        <v>8</v>
-      </c>
-      <c r="E27">
-        <v>0.0375772450062061</v>
-      </c>
-      <c r="F27">
-        <v>0.5318415352815214</v>
-      </c>
-      <c r="G27">
-        <v>0.5972669030519208</v>
-      </c>
-      <c r="H27">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I27">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28">
-        <v>6</v>
-      </c>
-      <c r="D28">
-        <v>8</v>
-      </c>
-      <c r="E28">
-        <v>-0.06992891923086383</v>
-      </c>
-      <c r="F28">
-        <v>-0.8520872125848641</v>
-      </c>
-      <c r="G28">
-        <v>0.3983594344092337</v>
-      </c>
-      <c r="H28">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I28">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29">
-        <v>6</v>
-      </c>
-      <c r="D29">
-        <v>8</v>
-      </c>
-      <c r="E29">
-        <v>0.007738359393570075</v>
-      </c>
-      <c r="F29">
-        <v>0.1074534130444508</v>
-      </c>
-      <c r="G29">
-        <v>0.914873162723242</v>
-      </c>
-      <c r="H29">
-        <v>0.9821698380463832</v>
-      </c>
-      <c r="I29">
-        <v>0.9821698380463832</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30">
-        <v>6</v>
-      </c>
-      <c r="D30">
-        <v>8</v>
-      </c>
-      <c r="E30">
-        <v>-0.03840427150753412</v>
-      </c>
-      <c r="F30">
-        <v>-0.4978842647102255</v>
-      </c>
-      <c r="G30">
-        <v>0.6208187835483427</v>
-      </c>
-      <c r="H30">
-        <v>0.9312281753225141</v>
-      </c>
-      <c r="I30">
-        <v>0.9312281753225141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31">
-        <v>6</v>
-      </c>
-      <c r="D31">
-        <v>8</v>
-      </c>
-      <c r="E31">
-        <v>-0.02733479004024534</v>
-      </c>
-      <c r="F31">
-        <v>-0.3776592617798687</v>
-      </c>
-      <c r="G31">
-        <v>0.7073337014983356</v>
-      </c>
-      <c r="H31">
-        <v>0.9645459565886394</v>
-      </c>
-      <c r="I31">
-        <v>0.9645459565886394</v>
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -10608,787 +9739,711 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B25" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B30" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B40" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B41" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B42" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B43" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B48" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C49" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B50" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B51" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C51" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B52" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B54" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B55" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C55" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C56" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C59" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B60" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="B61" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B62" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C62" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B63" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C63" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B64" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C64" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
